--- a/dados_all_stores/Keys Summary - All Stores (Stores) (2026-10-13).xlsx
+++ b/dados_all_stores/Keys Summary - All Stores (Stores) (2026-10-13).xlsx
@@ -915,36 +915,36 @@
   </si>
   <si>
     <t>215
-168</t>
-  </si>
-  <si>
-    <t>34</t>
-  </si>
-  <si>
-    <t>R$ 827.188,86</t>
-  </si>
-  <si>
-    <t>R$ 4.595,49
-R$ 4.680,74</t>
-  </si>
-  <si>
-    <t>(20.1%)
+171</t>
+  </si>
+  <si>
+    <t>30</t>
+  </si>
+  <si>
+    <t>R$ 840.743,70</t>
+  </si>
+  <si>
+    <t>R$ 4.569,26
+R$ 4.665,79</t>
+  </si>
+  <si>
+    <t>(20.3%)
 (18.4%)</t>
   </si>
   <si>
-    <t>48.7</t>
-  </si>
-  <si>
-    <t>(21.2%)</t>
-  </si>
-  <si>
-    <t>135.4%</t>
-  </si>
-  <si>
-    <t>88.4%</t>
-  </si>
-  <si>
-    <t>4.0%</t>
+    <t>48.4</t>
+  </si>
+  <si>
+    <t>(21.4%)</t>
+  </si>
+  <si>
+    <t>133.7%</t>
+  </si>
+  <si>
+    <t>86.9%</t>
+  </si>
+  <si>
+    <t>4.1%</t>
   </si>
   <si>
     <t>0.8%</t>
@@ -959,7 +959,7 @@
     <t>8.7%</t>
   </si>
   <si>
-    <t>5.3</t>
+    <t>5.4</t>
   </si>
   <si>
     <t>6.7</t>
@@ -971,10 +971,10 @@
     <t>18.6</t>
   </si>
   <si>
-    <t>75.1%</t>
-  </si>
-  <si>
-    <t>-R$ 22.748,80</t>
+    <t>74.8%</t>
+  </si>
+  <si>
+    <t>-R$ 24.816,86</t>
   </si>
   <si>
     <t>2.94</t>
@@ -6705,7 +6705,7 @@
         <v>19579</v>
       </c>
       <c r="B42" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C42" s="4">
         <v>44</v>
@@ -6741,25 +6741,61 @@
       <c t="s" r="N42" s="4">
         <v>52</v>
       </c>
-      <c r="O42" s="5"/>
-      <c r="P42" s="5"/>
-      <c r="Q42" s="6"/>
-      <c r="R42" s="7"/>
-      <c r="S42" s="6"/>
-      <c r="T42" s="6"/>
-      <c r="U42" s="6"/>
-      <c r="V42" s="6"/>
-      <c r="W42" s="6"/>
-      <c r="X42" s="8"/>
-      <c r="Y42" s="6"/>
-      <c r="Z42" s="6"/>
-      <c r="AA42" s="8"/>
-      <c r="AB42" s="8"/>
-      <c r="AC42" s="8"/>
-      <c r="AD42" s="8"/>
-      <c r="AE42" s="6"/>
+      <c r="O42" s="5">
+        <v>3382.6700000000001</v>
+      </c>
+      <c r="P42" s="5">
+        <v>3382.6700000000001</v>
+      </c>
+      <c r="Q42" s="6">
+        <v>-0.13399879162741157</v>
+      </c>
+      <c r="R42" s="7">
+        <v>33</v>
+      </c>
+      <c r="S42" s="6">
+        <v>-0.23255813953488369</v>
+      </c>
+      <c r="T42" s="6">
+        <v>0.34966171692775233</v>
+      </c>
+      <c r="U42" s="6">
+        <v>0.023448991477146752</v>
+      </c>
+      <c r="V42" s="6">
+        <v>0.095359435002527582</v>
+      </c>
+      <c r="W42" s="6">
+        <v>0.03509934460056701</v>
+      </c>
+      <c r="X42" s="8">
+        <v>26.482499999999998</v>
+      </c>
+      <c r="Y42" s="6">
+        <v>0.90000000000000002</v>
+      </c>
+      <c r="Z42" s="6">
+        <v>0</v>
+      </c>
+      <c r="AA42" s="8">
+        <v>7.1333333333333337</v>
+      </c>
+      <c r="AB42" s="8">
+        <v>5.788335</v>
+      </c>
+      <c r="AC42" s="8">
+        <v>13.397499</v>
+      </c>
+      <c r="AD42" s="8">
+        <v>20.344999999999999</v>
+      </c>
+      <c r="AE42" s="6">
+        <v>0.75</v>
+      </c>
       <c r="AF42" s="9"/>
-      <c r="AG42" s="5"/>
+      <c r="AG42" s="5">
+        <v>0</v>
+      </c>
       <c r="AH42" s="10">
         <v>3</v>
       </c>
@@ -11033,7 +11069,7 @@
         <v>-253</v>
       </c>
       <c r="AH76" s="10">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AI76" s="11"/>
       <c r="AJ76" s="13">
@@ -16471,7 +16507,7 @@
         <v>0</v>
       </c>
       <c r="AH120" s="10">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AI120" s="11"/>
       <c r="AJ120" s="13">
@@ -19080,7 +19116,7 @@
         <v>19793</v>
       </c>
       <c r="B141" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C141" s="4">
         <v>44</v>
@@ -19116,25 +19152,61 @@
       <c t="s" r="N141" s="4">
         <v>52</v>
       </c>
-      <c r="O141" s="5"/>
-      <c r="P141" s="5"/>
-      <c r="Q141" s="6"/>
-      <c r="R141" s="7"/>
-      <c r="S141" s="6"/>
-      <c r="T141" s="6"/>
-      <c r="U141" s="6"/>
-      <c r="V141" s="6"/>
-      <c r="W141" s="6"/>
-      <c r="X141" s="8"/>
-      <c r="Y141" s="6"/>
-      <c r="Z141" s="6"/>
-      <c r="AA141" s="8"/>
-      <c r="AB141" s="8"/>
-      <c r="AC141" s="8"/>
-      <c r="AD141" s="8"/>
-      <c r="AE141" s="6"/>
+      <c r="O141" s="5">
+        <v>2745.6999999999998</v>
+      </c>
+      <c r="P141" s="5">
+        <v>2745.6999999999998</v>
+      </c>
+      <c r="Q141" s="6">
+        <v>-0.047293546148508003</v>
+      </c>
+      <c r="R141" s="7">
+        <v>35</v>
+      </c>
+      <c r="S141" s="6">
+        <v>0.060606060606060552</v>
+      </c>
+      <c r="T141" s="6">
+        <v>0.39382037367520123</v>
+      </c>
+      <c r="U141" s="6">
+        <v>0.067794223695232539</v>
+      </c>
+      <c r="V141" s="6">
+        <v>0.14908948537713518</v>
+      </c>
+      <c r="W141" s="6">
+        <v>0.070450158429544385</v>
+      </c>
+      <c r="X141" s="8">
+        <v>23.036111111111111</v>
+      </c>
+      <c r="Y141" s="6">
+        <v>0.88888888888888884</v>
+      </c>
+      <c r="Z141" s="6">
+        <v>0.1111111111111111</v>
+      </c>
+      <c r="AA141" s="8">
+        <v>4.0562500000000004</v>
+      </c>
+      <c r="AB141" s="8">
+        <v>3.9000000000000004</v>
+      </c>
+      <c r="AC141" s="8">
+        <v>8.6324070000000006</v>
+      </c>
+      <c r="AD141" s="8">
+        <v>16.557405555555555</v>
+      </c>
+      <c r="AE141" s="6">
+        <v>0.88888888888888884</v>
+      </c>
       <c r="AF141" s="9"/>
-      <c r="AG141" s="5"/>
+      <c r="AG141" s="5">
+        <v>0</v>
+      </c>
       <c r="AH141" s="10">
         <v>4</v>
       </c>
@@ -21294,7 +21366,7 @@
         <v>19863</v>
       </c>
       <c r="B159" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C159" s="4">
         <v>44</v>
@@ -21330,27 +21402,61 @@
       <c t="s" r="N159" s="4">
         <v>52</v>
       </c>
-      <c r="O159" s="5"/>
-      <c r="P159" s="5"/>
-      <c r="Q159" s="6"/>
-      <c r="R159" s="7"/>
-      <c r="S159" s="6"/>
-      <c r="T159" s="6"/>
-      <c r="U159" s="6"/>
-      <c r="V159" s="6"/>
-      <c r="W159" s="6"/>
-      <c r="X159" s="8"/>
-      <c r="Y159" s="6"/>
-      <c r="Z159" s="6"/>
-      <c r="AA159" s="8"/>
-      <c r="AB159" s="8"/>
+      <c r="O159" s="5">
+        <v>5358.4099999999999</v>
+      </c>
+      <c r="P159" s="5">
+        <v>5358.4099999999999</v>
+      </c>
+      <c r="Q159" s="6">
+        <v>-0.2346025179907496</v>
+      </c>
+      <c r="R159" s="7">
+        <v>48</v>
+      </c>
+      <c r="S159" s="6">
+        <v>-0.2615384615384615</v>
+      </c>
+      <c r="T159" s="6">
+        <v>0.29644179896648448</v>
+      </c>
+      <c r="U159" s="6">
+        <v>-0.0077249221317517705</v>
+      </c>
+      <c r="V159" s="6">
+        <v>0.052864655746760705</v>
+      </c>
+      <c r="W159" s="6">
+        <v>0.010859657995562117</v>
+      </c>
+      <c r="X159" s="8">
+        <v>31.249493939393943</v>
+      </c>
+      <c r="Y159" s="6">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="Z159" s="6">
+        <v>0.15151515151515152</v>
+      </c>
+      <c r="AA159" s="8">
+        <v>5.1407808510638295</v>
+      </c>
+      <c r="AB159" s="8">
+        <v>7.8388878787878777</v>
+      </c>
       <c r="AC159" s="8">
         <v>13.394443000000001</v>
       </c>
-      <c r="AD159" s="8"/>
-      <c r="AE159" s="6"/>
+      <c r="AD159" s="8">
+        <v>20.322727272727271</v>
+      </c>
+      <c r="AE159" s="6">
+        <v>0.36363636363636365</v>
+      </c>
       <c r="AF159" s="9"/>
-      <c r="AG159" s="5"/>
+      <c r="AG159" s="5">
+        <v>0</v>
+      </c>
       <c r="AH159" s="10">
         <v>2</v>
       </c>
@@ -21594,7 +21700,9 @@
       <c r="AB161" s="8">
         <v>8.0333500000000004</v>
       </c>
-      <c r="AC161" s="8"/>
+      <c r="AC161" s="8">
+        <v>15.349999</v>
+      </c>
       <c r="AD161" s="8">
         <v>20.625</v>
       </c>
@@ -22587,7 +22695,7 @@
         <v>0.023690807799442895</v>
       </c>
       <c r="W169" s="6">
-        <v>-0.069969898463473804</v>
+        <v>-0.040429957767993532</v>
       </c>
       <c r="X169" s="8">
         <v>24.785604545454547</v>
@@ -27336,7 +27444,7 @@
         <v>19962</v>
       </c>
       <c r="B207" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C207" s="4">
         <v>44</v>
@@ -27372,25 +27480,57 @@
       <c t="s" r="N207" s="4">
         <v>52</v>
       </c>
-      <c r="O207" s="5"/>
-      <c r="P207" s="5"/>
+      <c r="O207" s="5">
+        <v>2068.0599999999999</v>
+      </c>
+      <c r="P207" s="5">
+        <v>2068.0599999999999</v>
+      </c>
       <c r="Q207" s="6"/>
-      <c r="R207" s="7"/>
+      <c r="R207" s="7">
+        <v>26</v>
+      </c>
       <c r="S207" s="6"/>
-      <c r="T207" s="6"/>
-      <c r="U207" s="6"/>
-      <c r="V207" s="6"/>
-      <c r="W207" s="6"/>
-      <c r="X207" s="8"/>
-      <c r="Y207" s="6"/>
-      <c r="Z207" s="6"/>
-      <c r="AA207" s="8"/>
-      <c r="AB207" s="8"/>
-      <c r="AC207" s="8"/>
-      <c r="AD207" s="8"/>
-      <c r="AE207" s="6"/>
+      <c r="T207" s="6">
+        <v>7.2531744726942157E-05</v>
+      </c>
+      <c r="U207" s="6">
+        <v>-0.49400404243590612</v>
+      </c>
+      <c r="V207" s="6">
+        <v>0.048345067357813611</v>
+      </c>
+      <c r="W207" s="6">
+        <v>-0.012262458536019266</v>
+      </c>
+      <c r="X207" s="8">
+        <v>35.110253846153846</v>
+      </c>
+      <c r="Y207" s="6">
+        <v>0.69230769230769229</v>
+      </c>
+      <c r="Z207" s="6">
+        <v>0.23076923076923078</v>
+      </c>
+      <c r="AA207" s="8">
+        <v>11.010869565217391</v>
+      </c>
+      <c r="AB207" s="8">
+        <v>8.5371769230769239</v>
+      </c>
+      <c r="AC207" s="8">
+        <v>21.334613999999998</v>
+      </c>
+      <c r="AD207" s="8">
+        <v>28.28717692307692</v>
+      </c>
+      <c r="AE207" s="6">
+        <v>0.23076923076923078</v>
+      </c>
       <c r="AF207" s="9"/>
-      <c r="AG207" s="5"/>
+      <c r="AG207" s="5">
+        <v>-2068.0599999999999</v>
+      </c>
       <c r="AH207" s="10">
         <v>4</v>
       </c>

--- a/dados_all_stores/Keys Summary - All Stores (Stores) (2026-10-13).xlsx
+++ b/dados_all_stores/Keys Summary - All Stores (Stores) (2026-10-13).xlsx
@@ -915,33 +915,33 @@
   </si>
   <si>
     <t>215
-171</t>
-  </si>
-  <si>
-    <t>30</t>
-  </si>
-  <si>
-    <t>R$ 840.743,70</t>
-  </si>
-  <si>
-    <t>R$ 4.569,26
-R$ 4.665,79</t>
-  </si>
-  <si>
-    <t>(20.3%)
-(18.4%)</t>
-  </si>
-  <si>
-    <t>48.4</t>
-  </si>
-  <si>
-    <t>(21.4%)</t>
-  </si>
-  <si>
-    <t>133.7%</t>
-  </si>
-  <si>
-    <t>86.9%</t>
+172</t>
+  </si>
+  <si>
+    <t>29</t>
+  </si>
+  <si>
+    <t>R$ 844.165,00</t>
+  </si>
+  <si>
+    <t>R$ 4.563,05
+R$ 4.658,56</t>
+  </si>
+  <si>
+    <t>(20.2%)
+(18.3%)</t>
+  </si>
+  <si>
+    <t>48.3</t>
+  </si>
+  <si>
+    <t>(21.3%)</t>
+  </si>
+  <si>
+    <t>133.1%</t>
+  </si>
+  <si>
+    <t>86.4%</t>
   </si>
   <si>
     <t>4.1%</t>
@@ -950,28 +950,28 @@
     <t>0.8%</t>
   </si>
   <si>
-    <t>26.7</t>
-  </si>
-  <si>
-    <t>76.7%</t>
-  </si>
-  <si>
-    <t>8.7%</t>
+    <t>27.0</t>
+  </si>
+  <si>
+    <t>76.4%</t>
+  </si>
+  <si>
+    <t>9.1%</t>
   </si>
   <si>
     <t>5.4</t>
   </si>
   <si>
-    <t>6.7</t>
+    <t>6.9</t>
   </si>
   <si>
     <t>12.0</t>
   </si>
   <si>
-    <t>18.6</t>
-  </si>
-  <si>
-    <t>74.8%</t>
+    <t>18.8</t>
+  </si>
+  <si>
+    <t>74.5%</t>
   </si>
   <si>
     <t>-R$ 24.816,86</t>
@@ -2216,10 +2216,10 @@
         <v>-0.33333333333333337</v>
       </c>
       <c r="T7" s="6">
-        <v>0.4922749836580062</v>
+        <v>0.44797156225898904</v>
       </c>
       <c r="U7" s="6">
-        <v>-0.019235657785290246</v>
+        <v>-0.063539079184307415</v>
       </c>
       <c r="V7" s="6">
         <v>0.032756569303412496</v>
@@ -11160,10 +11160,10 @@
         <v>-0.13888888888888884</v>
       </c>
       <c r="T77" s="6">
-        <v>0.33842477622920675</v>
+        <v>0.362426901540851</v>
       </c>
       <c r="U77" s="6">
-        <v>0.0063857031920546052</v>
+        <v>0.030387828503698863</v>
       </c>
       <c r="V77" s="6">
         <v>0.040119957493767122</v>
@@ -14253,7 +14253,7 @@
         <v>19719</v>
       </c>
       <c r="B102" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C102" s="4">
         <v>44</v>
@@ -14289,25 +14289,59 @@
       <c t="s" r="N102" s="4">
         <v>52</v>
       </c>
-      <c r="O102" s="5"/>
-      <c r="P102" s="5"/>
-      <c r="Q102" s="6"/>
-      <c r="R102" s="7"/>
-      <c r="S102" s="6"/>
-      <c r="T102" s="6"/>
-      <c r="U102" s="6"/>
-      <c r="V102" s="6"/>
-      <c r="W102" s="6"/>
-      <c r="X102" s="8"/>
-      <c r="Y102" s="6"/>
-      <c r="Z102" s="6"/>
-      <c r="AA102" s="8"/>
-      <c r="AB102" s="8"/>
+      <c r="O102" s="5">
+        <v>3421.3000000000002</v>
+      </c>
+      <c r="P102" s="5">
+        <v>3421.3000000000002</v>
+      </c>
+      <c r="Q102" s="6">
+        <v>0.12258424385602273</v>
+      </c>
+      <c r="R102" s="7">
+        <v>33</v>
+      </c>
+      <c r="S102" s="6">
+        <v>-0.10810810810810811</v>
+      </c>
+      <c r="T102" s="6">
+        <v>3.6886563586940638E-05</v>
+      </c>
+      <c r="U102" s="6">
+        <v>-0.36224937889106479</v>
+      </c>
+      <c r="V102" s="6">
+        <v>0.018266740712594626</v>
+      </c>
+      <c r="W102" s="6">
+        <v>-0.0062210270949639018</v>
+      </c>
+      <c r="X102" s="8">
+        <v>81.072916666666671</v>
+      </c>
+      <c r="Y102" s="6">
+        <v>0.041666666666666664</v>
+      </c>
+      <c r="Z102" s="6">
+        <v>0.83333333333333337</v>
+      </c>
+      <c r="AA102" s="8">
+        <v>8.6284935483870964</v>
+      </c>
+      <c r="AB102" s="8">
+        <v>53.952779166666666</v>
+      </c>
       <c r="AC102" s="8"/>
-      <c r="AD102" s="8"/>
-      <c r="AE102" s="6"/>
+      <c r="AD102" s="8">
+        <v>69.824304166666664</v>
+      </c>
+      <c r="AE102" s="6">
+        <v>0.041666666666666664</v>
+      </c>
       <c r="AF102" s="9"/>
-      <c r="AG102" s="5"/>
+      <c r="AG102" s="5">
+        <v>0</v>
+      </c>
       <c r="AH102" s="10">
         <v>2</v>
       </c>

--- a/dados_all_stores/Keys Summary - All Stores (Stores) (2026-10-13).xlsx
+++ b/dados_all_stores/Keys Summary - All Stores (Stores) (2026-10-13).xlsx
@@ -915,33 +915,33 @@
   </si>
   <si>
     <t>215
-172</t>
-  </si>
-  <si>
-    <t>29</t>
-  </si>
-  <si>
-    <t>R$ 844.165,00</t>
-  </si>
-  <si>
-    <t>R$ 4.563,05
-R$ 4.658,56</t>
-  </si>
-  <si>
-    <t>(20.2%)
-(18.3%)</t>
+173</t>
+  </si>
+  <si>
+    <t>28</t>
+  </si>
+  <si>
+    <t>R$ 847.947,41</t>
+  </si>
+  <si>
+    <t>R$ 4.558,86
+R$ 4.653,49</t>
+  </si>
+  <si>
+    <t>(20.3%)
+(18.4%)</t>
   </si>
   <si>
     <t>48.3</t>
   </si>
   <si>
-    <t>(21.3%)</t>
-  </si>
-  <si>
-    <t>133.1%</t>
-  </si>
-  <si>
-    <t>86.4%</t>
+    <t>(21.4%)</t>
+  </si>
+  <si>
+    <t>131.3%</t>
+  </si>
+  <si>
+    <t>84.6%</t>
   </si>
   <si>
     <t>4.1%</t>
@@ -953,7 +953,7 @@
     <t>27.0</t>
   </si>
   <si>
-    <t>76.4%</t>
+    <t>76.5%</t>
   </si>
   <si>
     <t>9.1%</t>
@@ -965,16 +965,16 @@
     <t>6.9</t>
   </si>
   <si>
-    <t>12.0</t>
-  </si>
-  <si>
-    <t>18.8</t>
-  </si>
-  <si>
-    <t>74.5%</t>
-  </si>
-  <si>
-    <t>-R$ 24.816,86</t>
+    <t>12.3</t>
+  </si>
+  <si>
+    <t>18.9</t>
+  </si>
+  <si>
+    <t>74.3%</t>
+  </si>
+  <si>
+    <t>-R$ 24.673,94</t>
   </si>
   <si>
     <t>2.94</t>
@@ -3928,7 +3928,7 @@
         <v>0.022987311222605337</v>
       </c>
       <c r="W20" s="6">
-        <v>0.00060931825637707991</v>
+        <v>0.00098670098670098662</v>
       </c>
       <c r="X20" s="8">
         <v>21.667576363636364</v>
@@ -4840,7 +4840,7 @@
         <v>-145.69999999999999</v>
       </c>
       <c r="AH27" s="10">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AI27" s="11"/>
       <c r="AJ27" s="13">
@@ -12632,7 +12632,7 @@
         <v>19693</v>
       </c>
       <c r="B89" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C89" s="4">
         <v>44</v>
@@ -12666,25 +12666,59 @@
       <c t="s" r="N89" s="4">
         <v>52</v>
       </c>
-      <c r="O89" s="5"/>
-      <c r="P89" s="5"/>
-      <c r="Q89" s="6"/>
-      <c r="R89" s="7"/>
-      <c r="S89" s="6"/>
-      <c r="T89" s="6"/>
-      <c r="U89" s="6"/>
-      <c r="V89" s="6"/>
-      <c r="W89" s="6"/>
-      <c r="X89" s="8"/>
-      <c r="Y89" s="6"/>
-      <c r="Z89" s="6"/>
-      <c r="AA89" s="8"/>
-      <c r="AB89" s="8"/>
+      <c r="O89" s="5">
+        <v>3782.4099999999999</v>
+      </c>
+      <c r="P89" s="5">
+        <v>3782.4099999999999</v>
+      </c>
+      <c r="Q89" s="6">
+        <v>-0.33206482966144202</v>
+      </c>
+      <c r="R89" s="7">
+        <v>41</v>
+      </c>
+      <c r="S89" s="6">
+        <v>-0.2931034482758621</v>
+      </c>
+      <c r="T89" s="6">
+        <v>-3.0934154679159582</v>
+      </c>
+      <c r="U89" s="6">
+        <v>-3.4247914953693543</v>
+      </c>
+      <c r="V89" s="6">
+        <v>0.03163789753093927</v>
+      </c>
+      <c r="W89" s="6">
+        <v>0.0049512083565768916</v>
+      </c>
+      <c r="X89" s="8">
+        <v>39.981250000000003</v>
+      </c>
+      <c r="Y89" s="6">
+        <v>1</v>
+      </c>
+      <c r="Z89" s="6">
+        <v>0.375</v>
+      </c>
+      <c r="AA89" s="8">
+        <v>9.0952999999999999</v>
+      </c>
+      <c r="AB89" s="8">
+        <v>13.264581250000001</v>
+      </c>
       <c r="AC89" s="8"/>
-      <c r="AD89" s="8"/>
-      <c r="AE89" s="6"/>
+      <c r="AD89" s="8">
+        <v>30.537500000000001</v>
+      </c>
+      <c r="AE89" s="6">
+        <v>0.3125</v>
+      </c>
       <c r="AF89" s="9"/>
-      <c r="AG89" s="5"/>
+      <c r="AG89" s="5">
+        <v>142.91999999999999</v>
+      </c>
       <c r="AH89" s="10">
         <v>2</v>
       </c>
@@ -14214,7 +14248,7 @@
         <v>0</v>
       </c>
       <c r="AH101" s="10">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AI101" s="11"/>
       <c r="AJ101" s="13">
@@ -14331,7 +14365,9 @@
       <c r="AB102" s="8">
         <v>53.952779166666666</v>
       </c>
-      <c r="AC102" s="8"/>
+      <c r="AC102" s="8">
+        <v>62.941665</v>
+      </c>
       <c r="AD102" s="8">
         <v>69.824304166666664</v>
       </c>
@@ -16013,7 +16049,9 @@
       <c r="Z116" s="6"/>
       <c r="AA116" s="8"/>
       <c r="AB116" s="8"/>
-      <c r="AC116" s="8"/>
+      <c r="AC116" s="8">
+        <v>34.827959</v>
+      </c>
       <c r="AD116" s="8"/>
       <c r="AE116" s="6"/>
       <c r="AF116" s="9"/>
@@ -20119,16 +20157,16 @@
         <v>-0.34782608695652173</v>
       </c>
       <c r="T148" s="6">
-        <v>0</v>
+        <v>0.19386435476043701</v>
       </c>
       <c r="U148" s="6">
-        <v>-0.31935297104558547</v>
+        <v>-0.12548861628514843</v>
       </c>
       <c r="V148" s="6">
         <v>0.03338723367578475</v>
       </c>
       <c r="W148" s="6">
-        <v>-0.0041937339446618989</v>
+        <v>0.0087423482436795128</v>
       </c>
       <c r="X148" s="8">
         <v>35.970921276595746</v>
@@ -24718,7 +24756,7 @@
         <v>19923</v>
       </c>
       <c r="B185" s="3">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c t="s" r="C185" s="4">
         <v>44</v>
@@ -25689,7 +25727,7 @@
         <v>0</v>
       </c>
       <c r="AH192" s="10">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AI192" s="11"/>
       <c r="AJ192" s="13">
@@ -27000,7 +27038,7 @@
         <v>19957</v>
       </c>
       <c r="B203" s="3">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c t="s" r="C203" s="4">
         <v>44</v>

--- a/dados_all_stores/Keys Summary - All Stores (Stores) (2026-10-13).xlsx
+++ b/dados_all_stores/Keys Summary - All Stores (Stores) (2026-10-13).xlsx
@@ -915,33 +915,33 @@
   </si>
   <si>
     <t>215
-173</t>
-  </si>
-  <si>
-    <t>28</t>
-  </si>
-  <si>
-    <t>R$ 847.947,41</t>
-  </si>
-  <si>
-    <t>R$ 4.558,86
-R$ 4.653,49</t>
-  </si>
-  <si>
-    <t>(20.3%)
-(18.4%)</t>
-  </si>
-  <si>
-    <t>48.3</t>
-  </si>
-  <si>
-    <t>(21.4%)</t>
-  </si>
-  <si>
-    <t>131.3%</t>
-  </si>
-  <si>
-    <t>84.6%</t>
+179</t>
+  </si>
+  <si>
+    <t>22</t>
+  </si>
+  <si>
+    <t>R$ 868.504,61</t>
+  </si>
+  <si>
+    <t>R$ 4.523,46
+R$ 4.612,35</t>
+  </si>
+  <si>
+    <t>(20.5%)
+(18.7%)</t>
+  </si>
+  <si>
+    <t>47.9</t>
+  </si>
+  <si>
+    <t>(21.5%)</t>
+  </si>
+  <si>
+    <t>128.8%</t>
+  </si>
+  <si>
+    <t>82.5%</t>
   </si>
   <si>
     <t>4.1%</t>
@@ -950,31 +950,31 @@
     <t>0.8%</t>
   </si>
   <si>
-    <t>27.0</t>
-  </si>
-  <si>
-    <t>76.5%</t>
-  </si>
-  <si>
-    <t>9.1%</t>
+    <t>26.9</t>
+  </si>
+  <si>
+    <t>76.4%</t>
+  </si>
+  <si>
+    <t>8.9%</t>
   </si>
   <si>
     <t>5.4</t>
   </si>
   <si>
-    <t>6.9</t>
-  </si>
-  <si>
-    <t>12.3</t>
-  </si>
-  <si>
-    <t>18.9</t>
-  </si>
-  <si>
-    <t>74.3%</t>
-  </si>
-  <si>
-    <t>-R$ 24.673,94</t>
+    <t>6.8</t>
+  </si>
+  <si>
+    <t>12.2</t>
+  </si>
+  <si>
+    <t>18.8</t>
+  </si>
+  <si>
+    <t>74.7%</t>
+  </si>
+  <si>
+    <t>-R$ 24.728,74</t>
   </si>
   <si>
     <t>2.94</t>
@@ -2069,7 +2069,7 @@
         <v>19507</v>
       </c>
       <c r="B6" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C6" s="4">
         <v>44</v>
@@ -2105,25 +2105,61 @@
       <c t="s" r="N6" s="4">
         <v>52</v>
       </c>
-      <c r="O6" s="5"/>
-      <c r="P6" s="5"/>
-      <c r="Q6" s="6"/>
-      <c r="R6" s="7"/>
-      <c r="S6" s="6"/>
-      <c r="T6" s="6"/>
-      <c r="U6" s="6"/>
-      <c r="V6" s="6"/>
-      <c r="W6" s="6"/>
-      <c r="X6" s="8"/>
-      <c r="Y6" s="6"/>
-      <c r="Z6" s="6"/>
-      <c r="AA6" s="8"/>
-      <c r="AB6" s="8"/>
-      <c r="AC6" s="8"/>
-      <c r="AD6" s="8"/>
-      <c r="AE6" s="6"/>
+      <c r="O6" s="5">
+        <v>8083.4399999999996</v>
+      </c>
+      <c r="P6" s="5">
+        <v>8083.4399999999996</v>
+      </c>
+      <c r="Q6" s="6">
+        <v>-0.36466227464147771</v>
+      </c>
+      <c r="R6" s="7">
+        <v>72</v>
+      </c>
+      <c r="S6" s="6">
+        <v>-0.34545454545454546</v>
+      </c>
+      <c r="T6" s="6">
+        <v>0.32518634393278112</v>
+      </c>
+      <c r="U6" s="6">
+        <v>-0.0040150851617628139</v>
+      </c>
+      <c r="V6" s="6">
+        <v>0.047587462763377969</v>
+      </c>
+      <c r="W6" s="6">
+        <v>0.018582484684738179</v>
+      </c>
+      <c r="X6" s="8">
+        <v>21.855813953488372</v>
+      </c>
+      <c r="Y6" s="6">
+        <v>0.95454545454545459</v>
+      </c>
+      <c r="Z6" s="6">
+        <v>0</v>
+      </c>
+      <c r="AA6" s="8">
+        <v>6.6711900000000002</v>
+      </c>
+      <c r="AB6" s="8">
+        <v>2.469379069767442</v>
+      </c>
+      <c r="AC6" s="8">
+        <v>8.8209289999999996</v>
+      </c>
+      <c r="AD6" s="8">
+        <v>15.773644186046512</v>
+      </c>
+      <c r="AE6" s="6">
+        <v>0.95348837209302328</v>
+      </c>
       <c r="AF6" s="9"/>
-      <c r="AG6" s="5"/>
+      <c r="AG6" s="5">
+        <v>0</v>
+      </c>
       <c r="AH6" s="10">
         <v>5</v>
       </c>
@@ -7878,7 +7914,7 @@
         <v>19602</v>
       </c>
       <c r="B51" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C51" s="4">
         <v>44</v>
@@ -7914,25 +7950,59 @@
       <c t="s" r="N51" s="4">
         <v>52</v>
       </c>
-      <c r="O51" s="5"/>
-      <c r="P51" s="5"/>
-      <c r="Q51" s="6"/>
-      <c r="R51" s="7"/>
-      <c r="S51" s="6"/>
-      <c r="T51" s="6"/>
-      <c r="U51" s="6"/>
-      <c r="V51" s="6"/>
-      <c r="W51" s="6"/>
-      <c r="X51" s="8"/>
-      <c r="Y51" s="6"/>
-      <c r="Z51" s="6"/>
-      <c r="AA51" s="8"/>
-      <c r="AB51" s="8"/>
+      <c r="O51" s="5">
+        <v>909.79999999999995</v>
+      </c>
+      <c r="P51" s="5">
+        <v>909.79999999999995</v>
+      </c>
+      <c r="Q51" s="6">
+        <v>-0.55554469956033214</v>
+      </c>
+      <c r="R51" s="7">
+        <v>10</v>
+      </c>
+      <c r="S51" s="6">
+        <v>-0.47368421052631582</v>
+      </c>
+      <c r="T51" s="6">
+        <v>0</v>
+      </c>
+      <c r="U51" s="6">
+        <v>-0.38206199164651578</v>
+      </c>
+      <c r="V51" s="6">
+        <v>0.059185535282479669</v>
+      </c>
+      <c r="W51" s="6">
+        <v>-0.081515717740162669</v>
+      </c>
+      <c r="X51" s="8">
+        <v>27.683350000000001</v>
+      </c>
+      <c r="Y51" s="6">
+        <v>1</v>
+      </c>
+      <c r="Z51" s="6">
+        <v>0</v>
+      </c>
+      <c r="AA51" s="8">
+        <v>3.0016699999999998</v>
+      </c>
+      <c r="AB51" s="8">
+        <v>13.63335</v>
+      </c>
       <c r="AC51" s="8"/>
-      <c r="AD51" s="8"/>
-      <c r="AE51" s="6"/>
+      <c r="AD51" s="8">
+        <v>26.033349999999999</v>
+      </c>
+      <c r="AE51" s="6">
+        <v>0.5</v>
+      </c>
       <c r="AF51" s="9"/>
-      <c r="AG51" s="5"/>
+      <c r="AG51" s="5">
+        <v>0</v>
+      </c>
       <c r="AH51" s="10">
         <v>2</v>
       </c>
@@ -8805,7 +8875,9 @@
       <c r="Z58" s="6"/>
       <c r="AA58" s="8"/>
       <c r="AB58" s="8"/>
-      <c r="AC58" s="8"/>
+      <c r="AC58" s="8">
+        <v>8.2563490000000002</v>
+      </c>
       <c r="AD58" s="8"/>
       <c r="AE58" s="6"/>
       <c r="AF58" s="9"/>
@@ -20498,7 +20570,7 @@
         <v>19821</v>
       </c>
       <c r="B151" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C151" s="4">
         <v>44</v>
@@ -20534,25 +20606,61 @@
       <c t="s" r="N151" s="4">
         <v>52</v>
       </c>
-      <c r="O151" s="5"/>
-      <c r="P151" s="5"/>
-      <c r="Q151" s="6"/>
-      <c r="R151" s="7"/>
-      <c r="S151" s="6"/>
-      <c r="T151" s="6"/>
-      <c r="U151" s="6"/>
-      <c r="V151" s="6"/>
-      <c r="W151" s="6"/>
-      <c r="X151" s="8"/>
-      <c r="Y151" s="6"/>
-      <c r="Z151" s="6"/>
-      <c r="AA151" s="8"/>
-      <c r="AB151" s="8"/>
-      <c r="AC151" s="8"/>
-      <c r="AD151" s="8"/>
-      <c r="AE151" s="6"/>
+      <c r="O151" s="5">
+        <v>2586.1199999999999</v>
+      </c>
+      <c r="P151" s="5">
+        <v>2586.1199999999999</v>
+      </c>
+      <c r="Q151" s="6">
+        <v>-0.24176046489126835</v>
+      </c>
+      <c r="R151" s="7">
+        <v>34</v>
+      </c>
+      <c r="S151" s="6">
+        <v>-0.12820512820512819</v>
+      </c>
+      <c r="T151" s="6">
+        <v>0.081688668739269638</v>
+      </c>
+      <c r="U151" s="6">
+        <v>-0.26459069958083925</v>
+      </c>
+      <c r="V151" s="6">
+        <v>0.078189527168112852</v>
+      </c>
+      <c r="W151" s="6">
+        <v>0.028133845297201983</v>
+      </c>
+      <c r="X151" s="8">
+        <v>26.970113793103447</v>
+      </c>
+      <c r="Y151" s="6">
+        <v>0.51724137931034486</v>
+      </c>
+      <c r="Z151" s="6">
+        <v>0.068965517241379309</v>
+      </c>
+      <c r="AA151" s="8">
+        <v>6.2759794117647054</v>
+      </c>
+      <c r="AB151" s="8">
+        <v>2.6890793103448276</v>
+      </c>
+      <c r="AC151" s="8">
+        <v>8.9919530000000005</v>
+      </c>
+      <c r="AD151" s="8">
+        <v>15.933334482758621</v>
+      </c>
+      <c r="AE151" s="6">
+        <v>0.72413793103448276</v>
+      </c>
       <c r="AF151" s="9"/>
-      <c r="AG151" s="5"/>
+      <c r="AG151" s="5">
+        <v>0</v>
+      </c>
       <c r="AH151" s="10">
         <v>5</v>
       </c>
@@ -21248,7 +21356,7 @@
         <v>19855</v>
       </c>
       <c r="B157" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C157" s="4">
         <v>44</v>
@@ -21284,25 +21392,61 @@
       <c t="s" r="N157" s="4">
         <v>52</v>
       </c>
-      <c r="O157" s="5"/>
-      <c r="P157" s="5"/>
-      <c r="Q157" s="6"/>
-      <c r="R157" s="7"/>
-      <c r="S157" s="6"/>
-      <c r="T157" s="6"/>
-      <c r="U157" s="6"/>
-      <c r="V157" s="6"/>
-      <c r="W157" s="6"/>
-      <c r="X157" s="8"/>
-      <c r="Y157" s="6"/>
-      <c r="Z157" s="6"/>
-      <c r="AA157" s="8"/>
-      <c r="AB157" s="8"/>
-      <c r="AC157" s="8"/>
-      <c r="AD157" s="8"/>
-      <c r="AE157" s="6"/>
+      <c r="O157" s="5">
+        <v>1445.96</v>
+      </c>
+      <c r="P157" s="5">
+        <v>1445.96</v>
+      </c>
+      <c r="Q157" s="6">
+        <v>-0.55081576102488905</v>
+      </c>
+      <c r="R157" s="7">
+        <v>22</v>
+      </c>
+      <c r="S157" s="6">
+        <v>-0.37142857142857144</v>
+      </c>
+      <c r="T157" s="6">
+        <v>0.28677356220089073</v>
+      </c>
+      <c r="U157" s="6">
+        <v>-0.072475656311377895</v>
+      </c>
+      <c r="V157" s="6">
+        <v>0.094706976679852825</v>
+      </c>
+      <c r="W157" s="6">
+        <v>0.029691346925226146</v>
+      </c>
+      <c r="X157" s="8">
+        <v>26.527378571428574</v>
+      </c>
+      <c r="Y157" s="6">
+        <v>0.7142857142857143</v>
+      </c>
+      <c r="Z157" s="6">
+        <v>0</v>
+      </c>
+      <c r="AA157" s="8">
+        <v>6.257938095238095</v>
+      </c>
+      <c r="AB157" s="8">
+        <v>2.7845214285714284</v>
+      </c>
+      <c r="AC157" s="8">
+        <v>9.0654749999999993</v>
+      </c>
+      <c r="AD157" s="8">
+        <v>16.010714285714286</v>
+      </c>
+      <c r="AE157" s="6">
+        <v>0.6428571428571429</v>
+      </c>
       <c r="AF157" s="9"/>
-      <c r="AG157" s="5"/>
+      <c r="AG157" s="5">
+        <v>0</v>
+      </c>
       <c r="AH157" s="10">
         <v>4</v>
       </c>
@@ -21343,7 +21487,7 @@
         <v>19859</v>
       </c>
       <c r="B158" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C158" s="4">
         <v>44</v>
@@ -21379,25 +21523,61 @@
       <c t="s" r="N158" s="4">
         <v>52</v>
       </c>
-      <c r="O158" s="5"/>
-      <c r="P158" s="5"/>
-      <c r="Q158" s="6"/>
-      <c r="R158" s="7"/>
-      <c r="S158" s="6"/>
-      <c r="T158" s="6"/>
-      <c r="U158" s="6"/>
-      <c r="V158" s="6"/>
-      <c r="W158" s="6"/>
-      <c r="X158" s="8"/>
-      <c r="Y158" s="6"/>
-      <c r="Z158" s="6"/>
-      <c r="AA158" s="8"/>
-      <c r="AB158" s="8"/>
-      <c r="AC158" s="8"/>
-      <c r="AD158" s="8"/>
-      <c r="AE158" s="6"/>
+      <c r="O158" s="5">
+        <v>1757.2</v>
+      </c>
+      <c r="P158" s="5">
+        <v>1757.2</v>
+      </c>
+      <c r="Q158" s="6">
+        <v>-0.51772839424852957</v>
+      </c>
+      <c r="R158" s="7">
+        <v>17</v>
+      </c>
+      <c r="S158" s="6">
+        <v>-0.57499999999999996</v>
+      </c>
+      <c r="T158" s="6">
+        <v>0.27582107898930114</v>
+      </c>
+      <c r="U158" s="6">
+        <v>-0.0025877532437969496</v>
+      </c>
+      <c r="V158" s="6">
+        <v>0.062247609833826545</v>
+      </c>
+      <c r="W158" s="6">
+        <v>-0.0038917027088549963</v>
+      </c>
+      <c r="X158" s="8">
+        <v>25.497438461538461</v>
+      </c>
+      <c r="Y158" s="6">
+        <v>0.69230769230769229</v>
+      </c>
+      <c r="Z158" s="6">
+        <v>0</v>
+      </c>
+      <c r="AA158" s="8">
+        <v>5.7509823529411763</v>
+      </c>
+      <c r="AB158" s="8">
+        <v>2.2487153846153847</v>
+      </c>
+      <c r="AC158" s="8">
+        <v>8.1012810000000002</v>
+      </c>
+      <c r="AD158" s="8">
+        <v>15.0359</v>
+      </c>
+      <c r="AE158" s="6">
+        <v>0.84615384615384615</v>
+      </c>
       <c r="AF158" s="9"/>
-      <c r="AG158" s="5"/>
+      <c r="AG158" s="5">
+        <v>0</v>
+      </c>
       <c r="AH158" s="10">
         <v>2</v>
       </c>
@@ -22218,7 +22398,7 @@
         <v>19877</v>
       </c>
       <c r="B165" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C165" s="4">
         <v>44</v>
@@ -22254,25 +22434,61 @@
       <c t="s" r="N165" s="4">
         <v>52</v>
       </c>
-      <c r="O165" s="5"/>
-      <c r="P165" s="5"/>
-      <c r="Q165" s="6"/>
-      <c r="R165" s="7"/>
-      <c r="S165" s="6"/>
-      <c r="T165" s="6"/>
-      <c r="U165" s="6"/>
-      <c r="V165" s="6"/>
-      <c r="W165" s="6"/>
-      <c r="X165" s="8"/>
-      <c r="Y165" s="6"/>
-      <c r="Z165" s="6"/>
-      <c r="AA165" s="8"/>
-      <c r="AB165" s="8"/>
-      <c r="AC165" s="8"/>
-      <c r="AD165" s="8"/>
-      <c r="AE165" s="6"/>
+      <c r="O165" s="5">
+        <v>5774.6800000000003</v>
+      </c>
+      <c r="P165" s="5">
+        <v>5774.6800000000003</v>
+      </c>
+      <c r="Q165" s="6">
+        <v>0.48151910944863929</v>
+      </c>
+      <c r="R165" s="7">
+        <v>58</v>
+      </c>
+      <c r="S165" s="6">
+        <v>0.13725490196078427</v>
+      </c>
+      <c r="T165" s="6">
+        <v>0.28697716583429728</v>
+      </c>
+      <c r="U165" s="6">
+        <v>-0.010289522536313701</v>
+      </c>
+      <c r="V165" s="6">
+        <v>0.017626691002791496</v>
+      </c>
+      <c r="W165" s="6">
+        <v>-0.009907302222807151</v>
+      </c>
+      <c r="X165" s="8">
+        <v>20.933739024390245</v>
+      </c>
+      <c r="Y165" s="6">
+        <v>0.65853658536585369</v>
+      </c>
+      <c r="Z165" s="6">
+        <v>0</v>
+      </c>
+      <c r="AA165" s="8">
+        <v>5.2389875000000004</v>
+      </c>
+      <c r="AB165" s="8">
+        <v>3.1723585365853659</v>
+      </c>
+      <c r="AC165" s="8">
+        <v>8.37073</v>
+      </c>
+      <c r="AD165" s="8">
+        <v>15.295121951219512</v>
+      </c>
+      <c r="AE165" s="6">
+        <v>1</v>
+      </c>
       <c r="AF165" s="9"/>
-      <c r="AG165" s="5"/>
+      <c r="AG165" s="5">
+        <v>-54.799999999999997</v>
+      </c>
       <c r="AH165" s="10">
         <v>3</v>
       </c>
